--- a/results/DailyStats.xlsx
+++ b/results/DailyStats.xlsx
@@ -3896,31 +3896,31 @@
         <v>20260811</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>102.56</v>
       </c>
       <c r="E74" t="n">
-        <v>2442</v>
+        <v>2548</v>
       </c>
       <c r="F74" t="n">
-        <v>80.16</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>2361.84</v>
+        <v>2464.4</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K74" t="n">
         <v>2</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>

--- a/results/DailyStats.xlsx
+++ b/results/DailyStats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R74"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3896,22 +3896,22 @@
         <v>20260811</v>
       </c>
       <c r="B74" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C74" t="n">
-        <v>3.44</v>
+        <v>4.7</v>
       </c>
       <c r="D74" t="n">
-        <v>102.56</v>
+        <v>141.3</v>
       </c>
       <c r="E74" t="n">
-        <v>2548</v>
+        <v>2588</v>
       </c>
       <c r="F74" t="n">
-        <v>83.59999999999999</v>
+        <v>84.86</v>
       </c>
       <c r="G74" t="n">
-        <v>2464.4</v>
+        <v>2503.14</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3939,6 +3939,111 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20260812</v>
+      </c>
+      <c r="B75" t="n">
+        <v>254</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="D75" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2842</v>
+      </c>
+      <c r="F75" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2748.66</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4</v>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>644	14/08/2026 11:00:00	12/08/2026 18:29:03	12/08/2026 18:30:40	Le Quellec Kiliann	Le Double 2	36 €	90	Réservant
+639	12/08/2026 20:00:00	12/08/2026 12:11:28	12/08/2026 12:12:29	Allione Philippe	Le Simple	20 €	60	Réservant</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>20260813</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2988</v>
+      </c>
+      <c r="F76" t="n">
+        <v>98.34</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2889.66</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Aucun créneau annulé aujourdhui !</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/DailyStats.xlsx
+++ b/results/DailyStats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4044,6 +4044,102 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20260905</v>
+      </c>
+      <c r="B77" t="n">
+        <v>170</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D77" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="E77" t="n">
+        <v>930</v>
+      </c>
+      <c r="F77" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="B78" t="n">
+        <v>50</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F78" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1952.2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
